--- a/kebs_banned_products (1).xlsx
+++ b/kebs_banned_products (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="kebs_banned_products (1)" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="251">
   <si>
     <t>Brand</t>
   </si>
@@ -96,7 +96,7 @@
     <t>Sivoclair Lightening Body Lotion</t>
   </si>
   <si>
-    <t>Clear</t>
+    <t>Clear Essence</t>
   </si>
   <si>
     <t>Clear Essence Skin Beautyfying Milk</t>
@@ -108,7 +108,7 @@
     <t>Princess Lotion</t>
   </si>
   <si>
-    <t>Peau</t>
+    <t>Peau Claire</t>
   </si>
   <si>
     <t>Peau Claire Beauty Body Lotion</t>
@@ -183,13 +183,7 @@
     <t>Contains Mercury and its compounds. Listed under: Skin Lightening Products - Creams (Mercury).</t>
   </si>
   <si>
-    <t>Cream</t>
-  </si>
-  <si>
-    <t>Cream Preparations Containing Hydrogen Peroxide(H2o2)</t>
-  </si>
-  <si>
-    <t>Hot</t>
+    <t>Hot Movate</t>
   </si>
   <si>
     <t>Hot Movate Gel</t>
@@ -219,16 +213,19 @@
     <t>Sivoclair Cream</t>
   </si>
   <si>
-    <t>Ultimate</t>
+    <t>Ultimate Lady</t>
   </si>
   <si>
     <t>Ultimate Lady Gel</t>
   </si>
   <si>
+    <t>Fair &amp; White</t>
+  </si>
+  <si>
     <t>Fair &amp; White Gel Plus</t>
   </si>
   <si>
-    <t>First</t>
+    <t>First Class</t>
   </si>
   <si>
     <t>First Class Lady Cream</t>
@@ -237,10 +234,13 @@
     <t>Jaribu Beta  ? Cream</t>
   </si>
   <si>
+    <t>Soft &amp; Beautiful</t>
+  </si>
+  <si>
     <t>Soft &amp; Beautiful Gel</t>
   </si>
   <si>
-    <t>Skin</t>
+    <t>Skin Balance</t>
   </si>
   <si>
     <t>Skin Balance Gel Wrinkle Remover</t>
@@ -261,13 +261,10 @@
     <t>Jolen Cream</t>
   </si>
   <si>
-    <t>Skin Preparations Containing Steroids</t>
-  </si>
-  <si>
     <t>Amira -C</t>
   </si>
   <si>
-    <t>Body</t>
+    <t>Body Clear</t>
   </si>
   <si>
     <t>Body Clear Cream Spot Remover</t>
@@ -297,13 +294,13 @@
     <t>Dermo -Gel Plus</t>
   </si>
   <si>
-    <t>Fashion</t>
+    <t>Fashion Fair</t>
   </si>
   <si>
     <t>Fashion Fair Gel Plus</t>
   </si>
   <si>
-    <t>Action</t>
+    <t>Action Demovate</t>
   </si>
   <si>
     <t>Action Demovate Cream</t>
@@ -312,6 +309,9 @@
     <t>Topifram Gel Plus</t>
   </si>
   <si>
+    <t>Peau Clair</t>
+  </si>
+  <si>
     <t>Peau Clair Gel Plus</t>
   </si>
   <si>
@@ -327,9 +327,6 @@
     <t>Body Treat Cream Spot Remover</t>
   </si>
   <si>
-    <t>Action Demovate</t>
-  </si>
-  <si>
     <t>Action Demovate Gel Plus</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>Ultra-Gel Plus</t>
   </si>
   <si>
-    <t>Skin Balance</t>
-  </si>
-  <si>
     <t>Skin Balance Cream Wrinkle Remover</t>
   </si>
   <si>
@@ -360,7 +354,7 @@
     <t>Skin Success Gel</t>
   </si>
   <si>
-    <t>Neu</t>
+    <t xml:space="preserve">Neu Clear </t>
   </si>
   <si>
     <t>Neu Clear Gel</t>
@@ -399,9 +393,6 @@
     <t>Age Renewal Cream</t>
   </si>
   <si>
-    <t>Fashion Fair</t>
-  </si>
-  <si>
     <t>Fashion Fair Cream</t>
   </si>
   <si>
@@ -417,9 +408,6 @@
     <t>Clair &amp; Lovely Gel</t>
   </si>
   <si>
-    <t>Peau Clair</t>
-  </si>
-  <si>
     <t>Peau Clair Cream</t>
   </si>
   <si>
@@ -648,7 +636,7 @@
     <t>Elegance Skin Lightening Cream</t>
   </si>
   <si>
-    <t>Fade</t>
+    <t>Fade Out</t>
   </si>
   <si>
     <t>Fade Out Cream</t>
@@ -678,6 +666,9 @@
     <t>Shirley Cream</t>
   </si>
   <si>
+    <t>Princess Patra</t>
+  </si>
+  <si>
     <t>Princess Patra Luxury Complexion Cream</t>
   </si>
   <si>
@@ -702,7 +693,7 @@
     <t>Fulani Creme Eclaircissante</t>
   </si>
   <si>
-    <t>Binti</t>
+    <t>Binti Jambo</t>
   </si>
   <si>
     <t>Binti Jambo Cream</t>
@@ -720,9 +711,6 @@
     <t>Nish Medicated Cream</t>
   </si>
   <si>
-    <t>Body Clear</t>
-  </si>
-  <si>
     <t>Body Clear Cream</t>
   </si>
   <si>
@@ -732,9 +720,6 @@
     <t>Symba Creme Skin Lite 'N' Smooth</t>
   </si>
   <si>
-    <t>Clear Essence</t>
-  </si>
-  <si>
     <t>Clear Essence Medicated Fade Cream</t>
   </si>
   <si>
@@ -762,9 +747,6 @@
     <t>Ultime Skin Lightening Cream</t>
   </si>
   <si>
-    <t>Peau Claire</t>
-  </si>
-  <si>
     <t>Peau Claire Crème Eclaircissante</t>
   </si>
   <si>
@@ -772,6 +754,9 @@
   </si>
   <si>
     <t>Immediat Claire Lighten</t>
+  </si>
+  <si>
+    <t>Immediat Claire</t>
   </si>
   <si>
     <t>FDA keywords</t>
@@ -1957,7 +1942,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="71.5714285714286" customWidth="1"/>
@@ -2403,7 +2388,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
         <v>49</v>
@@ -2414,7 +2399,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
@@ -2442,10 +2427,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
         <v>58</v>
-      </c>
-      <c r="B35" t="s">
-        <v>59</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
@@ -2459,7 +2444,7 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
         <v>49</v>
@@ -2470,10 +2455,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
         <v>49</v>
@@ -2484,7 +2469,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
         <v>62</v>
@@ -2512,10 +2497,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
         <v>49</v>
@@ -2526,7 +2511,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>67</v>
@@ -2540,10 +2525,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C42" t="s">
         <v>49</v>
@@ -2554,10 +2539,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C43" t="s">
         <v>49</v>
@@ -2568,10 +2553,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -2582,24 +2567,24 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
         <v>49</v>
@@ -2610,10 +2595,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
         <v>49</v>
@@ -2624,10 +2609,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
         <v>49</v>
@@ -2638,10 +2623,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
         <v>49</v>
@@ -2652,10 +2637,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
         <v>49</v>
@@ -2666,10 +2651,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
         <v>49</v>
@@ -2680,10 +2665,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>49</v>
@@ -2694,10 +2679,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
         <v>49</v>
@@ -2708,10 +2693,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
         <v>49</v>
@@ -2722,10 +2707,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>49</v>
@@ -2736,10 +2721,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
         <v>49</v>
@@ -2750,10 +2735,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
         <v>49</v>
@@ -2764,10 +2749,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
         <v>49</v>
@@ -2778,10 +2763,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
         <v>49</v>
@@ -2792,10 +2777,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
         <v>49</v>
@@ -2806,10 +2791,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
         <v>49</v>
@@ -2820,38 +2805,38 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="B63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
         <v>49</v>
@@ -2862,10 +2847,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C65" t="s">
         <v>49</v>
@@ -2876,10 +2861,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
         <v>49</v>
@@ -2890,10 +2875,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
         <v>49</v>
@@ -2904,10 +2889,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
         <v>49</v>
@@ -2918,10 +2903,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
         <v>49</v>
@@ -2932,10 +2917,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
         <v>49</v>
@@ -2946,10 +2931,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
         <v>49</v>
@@ -2960,10 +2945,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="B72" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C72" t="s">
         <v>49</v>
@@ -2974,10 +2959,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C73" t="s">
         <v>49</v>
@@ -2988,10 +2973,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C74" t="s">
         <v>49</v>
@@ -3002,7 +2987,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s">
         <v>126</v>
@@ -3044,58 +3029,58 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
         <v>131</v>
       </c>
-      <c r="B78" t="s">
-        <v>132</v>
-      </c>
       <c r="C78" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
         <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="D79" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
       </c>
       <c r="C81" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3106,10 +3091,10 @@
         <v>140</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3120,10 +3105,10 @@
         <v>142</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3134,10 +3119,10 @@
         <v>144</v>
       </c>
       <c r="C84" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3148,10 +3133,10 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3162,10 +3147,10 @@
         <v>148</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3176,52 +3161,52 @@
         <v>150</v>
       </c>
       <c r="C87" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s">
         <v>151</v>
       </c>
-      <c r="B88" t="s">
-        <v>152</v>
-      </c>
       <c r="C88" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
         <v>153</v>
       </c>
-      <c r="B89" t="s">
-        <v>154</v>
-      </c>
       <c r="C89" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="B90" t="s">
         <v>155</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3232,150 +3217,150 @@
         <v>157</v>
       </c>
       <c r="C91" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" t="s">
         <v>158</v>
       </c>
-      <c r="B92" t="s">
-        <v>159</v>
-      </c>
       <c r="C92" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
+        <v>159</v>
+      </c>
+      <c r="B93" t="s">
         <v>160</v>
       </c>
-      <c r="B93" t="s">
-        <v>161</v>
-      </c>
       <c r="C93" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="B94" t="s">
         <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B95" t="s">
         <v>163</v>
       </c>
-      <c r="B95" t="s">
-        <v>164</v>
-      </c>
       <c r="C95" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" t="s">
         <v>165</v>
       </c>
-      <c r="B96" t="s">
-        <v>166</v>
-      </c>
       <c r="C96" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
         <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D97" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98" t="s">
         <v>168</v>
       </c>
-      <c r="B98" t="s">
-        <v>169</v>
-      </c>
       <c r="C98" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>170</v>
+        <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C99" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D99" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C100" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s">
         <v>173</v>
       </c>
       <c r="C101" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3386,10 +3371,10 @@
         <v>175</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3400,10 +3385,10 @@
         <v>177</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3414,10 +3399,10 @@
         <v>179</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3428,10 +3413,10 @@
         <v>181</v>
       </c>
       <c r="C105" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3442,10 +3427,10 @@
         <v>183</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3456,10 +3441,10 @@
         <v>185</v>
       </c>
       <c r="C107" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3470,10 +3455,10 @@
         <v>187</v>
       </c>
       <c r="C108" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3484,10 +3469,10 @@
         <v>189</v>
       </c>
       <c r="C109" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3498,10 +3483,10 @@
         <v>191</v>
       </c>
       <c r="C110" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D110" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3512,10 +3497,10 @@
         <v>193</v>
       </c>
       <c r="C111" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3526,10 +3511,10 @@
         <v>195</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3540,10 +3525,10 @@
         <v>197</v>
       </c>
       <c r="C113" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D113" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3554,38 +3539,38 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
+        <v>198</v>
+      </c>
+      <c r="B115" t="s">
         <v>200</v>
       </c>
-      <c r="B115" t="s">
-        <v>201</v>
-      </c>
       <c r="C115" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>202</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3593,223 +3578,223 @@
         <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
+        <v>205</v>
+      </c>
+      <c r="B119" t="s">
         <v>206</v>
       </c>
-      <c r="B119" t="s">
-        <v>207</v>
-      </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C120" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>209</v>
+        <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C121" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B122" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="B124" t="s">
         <v>213</v>
       </c>
       <c r="C124" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
+        <v>161</v>
+      </c>
+      <c r="B125" t="s">
         <v>214</v>
       </c>
-      <c r="B125" t="s">
-        <v>215</v>
-      </c>
       <c r="C125" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="B126" t="s">
         <v>216</v>
       </c>
       <c r="C126" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="B127" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C127" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D127" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C128" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D128" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D129" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B130" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D130" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="B132" t="s">
         <v>227</v>
       </c>
       <c r="C132" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D132" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3820,136 +3805,116 @@
         <v>229</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D133" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" t="s">
         <v>230</v>
       </c>
-      <c r="B134" t="s">
-        <v>231</v>
-      </c>
       <c r="C134" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
+        <v>231</v>
+      </c>
+      <c r="B135" t="s">
         <v>232</v>
       </c>
-      <c r="B135" t="s">
-        <v>233</v>
-      </c>
       <c r="C135" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D135" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
+        <v>233</v>
+      </c>
+      <c r="B136" t="s">
         <v>234</v>
       </c>
-      <c r="B136" t="s">
-        <v>235</v>
-      </c>
       <c r="C136" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
+        <v>235</v>
+      </c>
+      <c r="B137" t="s">
         <v>236</v>
       </c>
-      <c r="B137" t="s">
-        <v>237</v>
-      </c>
       <c r="C137" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
+        <v>237</v>
+      </c>
+      <c r="B138" t="s">
         <v>238</v>
       </c>
-      <c r="B138" t="s">
-        <v>239</v>
-      </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D138" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D139" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D140" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>245</v>
-      </c>
-      <c r="C141" t="s">
-        <v>136</v>
-      </c>
-      <c r="D141" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" t="s">
-        <v>246</v>
-      </c>
-      <c r="B142" t="s">
-        <v>247</v>
-      </c>
-      <c r="C142" t="s">
-        <v>136</v>
-      </c>
-      <c r="D142" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3969,42 +3934,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="2" ht="30" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" ht="30" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" ht="30" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" ht="30" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="6" ht="45" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
